--- a/Excel/3_3_Enteric_Dairy_WIP_v02.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A35B965-CEC1-4157-883B-6CB329B7F1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1E325B-50EC-47F3-A75E-AD0DB9987CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="30" windowWidth="37920" windowHeight="20415" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="405" yWindow="345" windowWidth="37995" windowHeight="20115" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -6374,6 +6374,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Milk production converted from milk solids</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -6557,8 +6558,8 @@
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4845044" cy="234103"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -6857,7 +6858,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="9" name="TextBox 8">
@@ -6922,8 +6923,8 @@
       <xdr:rowOff>214312</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1461105" cy="370551"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -7128,7 +7129,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -7193,8 +7194,8 @@
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2591542" cy="194990"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -7342,7 +7343,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="TextBox 12">
@@ -7407,8 +7408,8 @@
       <xdr:rowOff>125505</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1353126" cy="186333"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -7552,7 +7553,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -7617,8 +7618,8 @@
       <xdr:rowOff>162728</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7606378" cy="332079"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -8155,7 +8156,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -8220,8 +8221,8 @@
       <xdr:rowOff>211708</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8183202" cy="332079"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -8776,7 +8777,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -8862,8 +8863,8 @@
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1606465" cy="383888"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -9086,7 +9087,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -9823,21 +9824,21 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
-  <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D8:F26" totalsRowShown="0">
+  <autoFilter ref="D8:F26" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FA4B4DF7-A993-40F2-870A-87A35A1D1CD3}" name="Symbol">
-      <calculatedColumnFormula array="1">InputFunctions_Utilities.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8A23F85B-E11F-43B7-AF58-1032F42D9585}" name="Manure management system">
-      <calculatedColumnFormula array="1">InputFunctions_Utilities.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{58D0574C-2490-473B-A8E1-317E3A493B21}" name="Symbol and MMS">
-      <calculatedColumnFormula array="1">InputFunctions_Utilities.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -18801,11 +18802,11 @@
         <v>Site</v>
       </c>
       <c r="D8" s="39" t="str">
-        <f>'Constants - Livestock'!$E$10</f>
+        <f>'Constants - Livestock'!$E$9</f>
         <v>Anaerobic lagoon</v>
       </c>
       <c r="E8" s="39" t="str">
-        <f>'Constants - Livestock'!$F$10</f>
+        <f>'Constants - Livestock'!$F$9</f>
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="G8" s="39" t="str">
@@ -18823,11 +18824,11 @@
         <v>Dairy</v>
       </c>
       <c r="D9" s="39" t="str">
-        <f>'Constants - Livestock'!$E$13</f>
+        <f>'Constants - Livestock'!$E$12</f>
         <v>Sump and dispersal system</v>
       </c>
       <c r="E9" s="39" t="str">
-        <f>'Constants - Livestock'!$F$13</f>
+        <f>'Constants - Livestock'!$F$12</f>
         <v>Sump and dispersal system (m=3a)</v>
       </c>
       <c r="G9" s="1" t="str">
@@ -18842,11 +18843,11 @@
     <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="D10" s="39" t="str">
-        <f>'Constants - Livestock'!$E$14</f>
+        <f>'Constants - Livestock'!$E$13</f>
         <v>Drains to paddock</v>
       </c>
       <c r="E10" s="39" t="str">
-        <f>'Constants - Livestock'!$F$14</f>
+        <f>'Constants - Livestock'!$F$13</f>
         <v>Drains to paddock (m=3b)</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -18859,11 +18860,11 @@
         <v>73</v>
       </c>
       <c r="D11" s="39" t="str">
-        <f>'Constants - Livestock'!$E$15</f>
+        <f>'Constants - Livestock'!$E$14</f>
         <v>Solid storage</v>
       </c>
       <c r="E11" s="39" t="str">
-        <f>'Constants - Livestock'!$F$15</f>
+        <f>'Constants - Livestock'!$F$14</f>
         <v>Solid storage (m=4)</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -25189,12 +25190,19 @@
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
+      <c r="D5" s="6" t="str" cm="1">
+        <f t="array" ref="D5">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title()</f>
+        <v>Table 5.12 Additional symbols used in algorithms for manure related emissions</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
-      <c r="D6" s="6" t="str" cm="1">
-        <f t="array" ref="D6">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title()</f>
-        <v>Table 5.12 Additional symbols used in algorithms for manure related emissions</v>
+      <c r="D6" s="3" t="str" cm="1">
+        <f t="array" ref="D6">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable()</f>
+        <v>MMS</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -25205,9 +25213,9 @@
       <c r="A7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="str" cm="1">
-        <f t="array" ref="D7">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable()</f>
-        <v>MMS</v>
+      <c r="D7" s="5" t="str" cm="1">
+        <f t="array" ref="D7">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Source()</f>
+        <v>National Inventory Report 2023 Volume 1: Table 5.12</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -25219,12 +25227,15 @@
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
-      <c r="D8" s="5" t="str" cm="1">
-        <f t="array" ref="D8">CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Source()</f>
-        <v>National Inventory Report 2023 Volume 1: Table 5.12</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="D8" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>77</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
@@ -25233,14 +25244,17 @@
         <f>HYPERLINK("#'Input - Dairy'!A1", "Dairy")</f>
         <v>Dairy</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>77</v>
+      <c r="D9" s="38" t="str" cm="1">
+        <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="38" t="str" cm="1">
+        <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
+        <v>Anaerobic lagoon</v>
+      </c>
+      <c r="F9" s="38" t="str" cm="1">
+        <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
+        <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -25248,15 +25262,15 @@
       <c r="A10" s="17"/>
       <c r="D10" s="38" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="38" t="str" cm="1">
         <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Anaerobic lagoon</v>
+        <v>Liquid systems</v>
       </c>
       <c r="F10" s="38" t="str" cm="1">
         <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Anaerobic lagoon (m=1)</v>
+        <v>Liquid systems (m=2)</v>
       </c>
       <c r="G10" s="3"/>
     </row>
@@ -25264,17 +25278,17 @@
       <c r="A11" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="38" t="str" cm="1">
+      <c r="D11" s="39" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>2</v>
-      </c>
-      <c r="E11" s="38" t="str" cm="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="39" t="str" cm="1">
         <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Liquid systems</v>
-      </c>
-      <c r="F11" s="38" t="str" cm="1">
+        <v>Daily spread</v>
+      </c>
+      <c r="F11" s="39" t="str" cm="1">
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Liquid systems (m=2)</v>
+        <v>Daily spread (m=3)</v>
       </c>
       <c r="G11" s="3"/>
     </row>
@@ -25285,15 +25299,15 @@
       </c>
       <c r="D12" s="39" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>3</v>
+        <v>3a</v>
       </c>
       <c r="E12" s="39" t="str" cm="1">
         <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Daily spread</v>
+        <v>Sump and dispersal system</v>
       </c>
       <c r="F12" s="39" t="str" cm="1">
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Daily spread (m=3)</v>
+        <v>Sump and dispersal system (m=3a)</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -25301,15 +25315,15 @@
       <c r="A13" s="17"/>
       <c r="D13" s="39" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>3a</v>
+        <v>3b</v>
       </c>
       <c r="E13" s="39" t="str" cm="1">
         <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Sump and dispersal system</v>
+        <v>Drains to paddock</v>
       </c>
       <c r="F13" s="39" t="str" cm="1">
         <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Sump and dispersal system (m=3a)</v>
+        <v>Drains to paddock (m=3b)</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -25319,15 +25333,15 @@
       </c>
       <c r="D14" s="39" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>3b</v>
+        <v>4</v>
       </c>
       <c r="E14" s="39" t="str" cm="1">
         <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Drains to paddock</v>
+        <v>Solid storage</v>
       </c>
       <c r="F14" s="39" t="str" cm="1">
         <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Drains to paddock (m=3b)</v>
+        <v>Solid storage (m=4)</v>
       </c>
       <c r="G14" s="3"/>
     </row>
@@ -25338,15 +25352,15 @@
       </c>
       <c r="D15" s="39" t="str" cm="1">
         <f t="array" ref="D15">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="39" t="str" cm="1">
         <f t="array" ref="E15">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Solid storage</v>
+        <v>Drylot (feed pad)</v>
       </c>
       <c r="F15" s="39" t="str" cm="1">
         <f t="array" ref="F15">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Solid storage (m=4)</v>
+        <v>Drylot (feed pad) (m=5)</v>
       </c>
       <c r="G15" s="3"/>
     </row>
@@ -25357,15 +25371,15 @@
       </c>
       <c r="D16" s="39" t="str" cm="1">
         <f t="array" ref="D16">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="39" t="str" cm="1">
         <f t="array" ref="E16">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Drylot (feed pad)</v>
+        <v>Composting (passive windrow)</v>
       </c>
       <c r="F16" s="39" t="str" cm="1">
         <f t="array" ref="F16">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Drylot (feed pad) (m=5)</v>
+        <v>Composting (passive windrow) (m=6)</v>
       </c>
       <c r="G16" s="3"/>
     </row>
@@ -25376,15 +25390,15 @@
       </c>
       <c r="D17" s="39" t="str" cm="1">
         <f t="array" ref="D17">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="39" t="str" cm="1">
         <f t="array" ref="E17">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Composting (passive windrow)</v>
+        <v>Digester / covered lagoons</v>
       </c>
       <c r="F17" s="39" t="str" cm="1">
         <f t="array" ref="F17">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Composting (passive windrow) (m=6)</v>
+        <v>Digester / covered lagoons (m=7)</v>
       </c>
       <c r="G17" s="3"/>
     </row>
@@ -25395,153 +25409,139 @@
       </c>
       <c r="D18" s="39" t="str" cm="1">
         <f t="array" ref="D18">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="39" t="str" cm="1">
         <f t="array" ref="E18">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Digester / covered lagoons</v>
+        <v>Deep litter</v>
       </c>
       <c r="F18" s="39" t="str" cm="1">
         <f t="array" ref="F18">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Digester / covered lagoons (m=7)</v>
+        <v>Deep litter (m=8)</v>
       </c>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="39" t="str" cm="1">
         <f t="array" ref="D19">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="39" t="str" cm="1">
         <f t="array" ref="E19">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Deep litter</v>
+        <v>Pit storage</v>
       </c>
       <c r="F19" s="39" t="str" cm="1">
         <f t="array" ref="F19">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Deep litter (m=8)</v>
+        <v>Pit storage (m=9)</v>
       </c>
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="39" t="str" cm="1">
         <f t="array" ref="D20">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="39" t="str" cm="1">
         <f t="array" ref="E20">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Pit storage</v>
+        <v>Poultry manure with bedding</v>
       </c>
       <c r="F20" s="39" t="str" cm="1">
         <f t="array" ref="F20">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Pit storage (m=9)</v>
+        <v>Poultry manure with bedding (m=10)</v>
       </c>
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="39" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="39" t="str" cm="1">
         <f t="array" ref="E21">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Poultry manure with bedding</v>
+        <v>Poultry manure without bedding</v>
       </c>
       <c r="F21" s="39" t="str" cm="1">
         <f t="array" ref="F21">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Poultry manure with bedding (m=10)</v>
+        <v>Poultry manure without bedding (m=11)</v>
       </c>
       <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="39" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>11</v>
+        <v>11a</v>
       </c>
       <c r="E22" s="39" t="str" cm="1">
         <f t="array" ref="E22">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Poultry manure without bedding</v>
+        <v>Belt manure removal</v>
       </c>
       <c r="F22" s="39" t="str" cm="1">
         <f t="array" ref="F22">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Poultry manure without bedding (m=11)</v>
+        <v>Belt manure removal (m=11a)</v>
       </c>
       <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="39" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>11a</v>
+        <v>11b</v>
       </c>
       <c r="E23" s="39" t="str" cm="1">
         <f t="array" ref="E23">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Belt manure removal</v>
+        <v>Manure stored in house</v>
       </c>
       <c r="F23" s="39" t="str" cm="1">
         <f t="array" ref="F23">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Belt manure removal (m=11a)</v>
+        <v>Manure stored in house (m=11b)</v>
       </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="39" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>11b</v>
+        <v>12</v>
       </c>
       <c r="E24" s="39" t="str" cm="1">
         <f t="array" ref="E24">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Manure stored in house</v>
+        <v>Direct processing</v>
       </c>
       <c r="F24" s="39" t="str" cm="1">
         <f t="array" ref="F24">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Manure stored in house (m=11b)</v>
+        <v>Direct processing (m=12)</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="39" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="39" t="str" cm="1">
         <f t="array" ref="E25">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Direct processing</v>
+        <v>Direct application</v>
       </c>
       <c r="F25" s="39" t="str" cm="1">
         <f t="array" ref="F25">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Direct processing (m=12)</v>
+        <v>Direct application (m=13)</v>
       </c>
       <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="39" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="39" t="str" cm="1">
         <f t="array" ref="E26">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Direct application</v>
+        <v>Pasture range and paddock</v>
       </c>
       <c r="F26" s="39" t="str" cm="1">
         <f t="array" ref="F26">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Direct application (m=13)</v>
+        <v>Pasture range and paddock (m=14)</v>
       </c>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="39" t="str" cm="1">
-        <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>14</v>
-      </c>
-      <c r="E27" s="39" t="str" cm="1">
-        <f t="array" ref="E27">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Pasture range and paddock</v>
-      </c>
-      <c r="F27" s="39" t="str" cm="1">
-        <f t="array" ref="F27">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
-        <v>Pasture range and paddock (m=14)</v>
-      </c>
-      <c r="G27" s="3"/>
-    </row>
+    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -25786,12 +25786,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQwBvAHcAcwAgAGEAbgBkACAASABlAGkAZgBlAHIAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAJwBSAGUAZgBlAHIAZQBuAGMAZQAnACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAJwBEAGEAaQByAHkAIABBAHUAcwB0AHIAYQBsAGkAYQAgAFsAMQBdACcAIABhAG4AZAAgAGkAcwAgAG4AbwB0ACAAdQBzAGUAZAAgAGkAbgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBkAGkAdQBtACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANQA1ADAALAAgADMAOAAwACwAIAAxADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAcgBnAGUAIABGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADAAMAAsACAANAAxADUALAAgADEANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBsAHMAdABlAGkAbgAtAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADYANQAwACwAIAA0ADUAMAAsACAAMQA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGkAZQBzAGkAYQBuACAAYwByAG8AcwBzAGIAcgBlAGQAXAAiACwAIAA1ADAAMAAsACAAMwA1ADAALAAgADEANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAZQByAHMAZQB5AFwAIgAsACAANAAwADAALAAgADIANwA1ACwAIAAxADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANAA1ADAALAAgADMAMQA1ACwAIAAxADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHkAcgBzAGgAaQByAGUAXAAiACwAIAA1ADQAMAAsACAAMwA3ADUALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAdQBlAHIAbgBzAGUAeQBcACIALAAgADQAOAAwACwAIAAzADMANQAsACAAMQA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAG8AdwBuACAAUwB3AGkAcwBzAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGwAbABhAHcAYQByAHIAYQAvAEEAdQBzAHMAaQBlACAAUgBlAGQAXAAiACwAIAA1ADUAMAAsACAAMwA3ADUALAAgADEANQAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABCAHUAbABsAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAwAC4AMAAxADYALAAgADAALgA2ACwAIAAwAC4ANQA3ACwAIAAwAC4AMQAsACAAMAAuADgAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAA1ADkAMAAsACAANQA5ADAALAAgADUAOQAwACwAIAA3ADcAMAAsACAANwA3ADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAPQAzACwANQA7ACAATgBQAFcAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAAnAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagAnACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEMASAA0ACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAPQAzACwANQApAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAEUAeABjAHIAZQB0AGUAZAAgACgATgBQAFcAagA9ADMALAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzADwAMQBcACIALAAgADAALgAwADEANwA2ACwAIAAwAC4AMgA2ADgANQAsACAAMAAuADAAMQAzADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzADwAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMQAwACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwAC4ANwAyACwAIAAwAC4ANwA2ACwAIAAwAC4AOAAsACAAMAAuADcAOAAsACAAMAAuADcANAAsACAAMAAuADYAOQAsACAAMAAuADcAMwAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AcwBcACIALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzACAAKABhACkAXAAiACwAIAAwAC4AMQA1ACwAIAAwAC4AMQA4ACwAIAAwAC4ANQAwACwAIAAwAC4AMgA0ACwAIAAwAC4AMQA3ACwAIAAwAC4AMQAzACwAIAAwAC4AMQA3ACwAIAAwAC4AMQA4ACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQA7ACAARgByAGEAYwBHAEEAUwBNAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZAApAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAEQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAMAAuADAANwAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABQAGEAZABkAG8AYwBrAFwAIgAsACAAMAAsACAAMAAuADIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAMAAuADMALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMQA3ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIAAnAEEAbgBuAHUAYQBsACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABpAG0AZQAgAHMAcABlAG4AdAAgAHAAZQByACAAYQByAGUAYQAnACAAcgBvAHcAIABhAHMAIAB0AGgAaQBzACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAaQBzACAAaQBuACAAdABoAGUAIAB0AGEAYgBsAGUAIAB0AGkAdABsAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHIAZQBhAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAFMAaABlAGQAXAAiACwAIABcACIARgBlAGUAZABwAGEAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAxADoAIABHAHIAYQB6AGUAZAAgAE8AbgBsAHkAXAAiACwAIAAwAC4AOAA5ACwAIAAwAC4AMQAxACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMgA6ACAATwBuACAAZgBlAGUAZABwAGEAZAAgAGYAbwByACAAPAAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAPAAzACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADcAOQAsACAAMAAuADEAMQAsACAAMAAuADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADMAOgAgAFAAYQBzAHQAdQByAGUALQBnAHIAYQB6AGUAZAAgADMALQA5ACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADUAMwA0ACwAIAAwAC4AMQAxACwAIAAwAC4AMwA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAA0ADoAIABaAGUAcgBvACAAZwByAGEAegBpAG4AZwBcACIALAAgADAALAAgADAALgAxADEALAAgADAALgA4ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgADwAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXABuAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBQAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcAG4ARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABNAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADcANQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AFwAbgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AZQB0ACAAZQBuAGUAcgBnAHkAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAgAC8AIABrAGcAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMwAuADAANQA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXABuAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBFAEMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcARABNAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQA4AC4ANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AFwAbgBFAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAdQBzAGUAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAA4ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBfAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAxADEAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAXwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHoAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4ARgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBDAF8AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQALgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAFwAbgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADIAIABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAzACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARABhAGkAcgB5ACAAQwBhAHQAdABsAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAzAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAxADIANAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAMQAyADQAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANAAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAMQAyADQAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGQAYQB5AHMAKQBcAG4ATgBfAGoAMwA1ACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADMANQAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABkAGEAeQBzACkAXABuAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoAMQAyADQALAAgAE0AXwBqADEAMgA0ACwAIABEAF8AagAxADIANAAsACAATgBfAGoAMwA1ACwAIABNAF8AagAzADUALAAgAEQAXwBqADMANQAsACAARABQAFcAXwBqADMANQAsACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUALABcAG4AIAAgACAAIAAoACgATgBfAGoAMQAyADQAIAAqACAATQBfAGoAMQAyADQAIAAqACAARABfAGoAMQAyADQAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAF8AagAzADUAIAAqACAARABfAGoAMwA1ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAIAAqACAARABQAFcAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAFAAVwBfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADEAMgA0AFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMQAyADQAXAAiACwAIABcACIAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMQAyADQAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADMANQBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMwA1AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagAzADUAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAFAAVwBfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBEAFAAVwAnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25806,7 +25801,12 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQwBvAHcAcwAgAGEAbgBkACAASABlAGkAZgBlAHIAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAJwBSAGUAZgBlAHIAZQBuAGMAZQAnACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAJwBEAGEAaQByAHkAIABBAHUAcwB0AHIAYQBsAGkAYQAgAFsAMQBdACcAIABhAG4AZAAgAGkAcwAgAG4AbwB0ACAAdQBzAGUAZAAgAGkAbgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBkAGkAdQBtACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANQA1ADAALAAgADMAOAAwACwAIAAxADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAcgBnAGUAIABGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADAAMAAsACAANAAxADUALAAgADEANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBsAHMAdABlAGkAbgAtAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADYANQAwACwAIAA0ADUAMAAsACAAMQA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGkAZQBzAGkAYQBuACAAYwByAG8AcwBzAGIAcgBlAGQAXAAiACwAIAA1ADAAMAAsACAAMwA1ADAALAAgADEANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAZQByAHMAZQB5AFwAIgAsACAANAAwADAALAAgADIANwA1ACwAIAAxADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANAA1ADAALAAgADMAMQA1ACwAIAAxADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHkAcgBzAGgAaQByAGUAXAAiACwAIAA1ADQAMAAsACAAMwA3ADUALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAdQBlAHIAbgBzAGUAeQBcACIALAAgADQAOAAwACwAIAAzADMANQAsACAAMQA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAG8AdwBuACAAUwB3AGkAcwBzAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGwAbABhAHcAYQByAHIAYQAvAEEAdQBzAHMAaQBlACAAUgBlAGQAXAAiACwAIAA1ADUAMAAsACAAMwA3ADUALAAgADEANQAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABCAHUAbABsAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAwAC4AMAAxADYALAAgADAALgA2ACwAIAAwAC4ANQA3ACwAIAAwAC4AMQAsACAAMAAuADgAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAA1ADkAMAAsACAANQA5ADAALAAgADUAOQAwACwAIAA3ADcAMAAsACAANwA3ADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAPQAzACwANQA7ACAATgBQAFcAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAAnAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagAnACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEMASAA0ACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAPQAzACwANQApAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAEUAeABjAHIAZQB0AGUAZAAgACgATgBQAFcAagA9ADMALAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzADwAMQBcACIALAAgADAALgAwADEANwA2ACwAIAAwAC4AMgA2ADgANQAsACAAMAAuADAAMQAzADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzADwAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMQAwACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwAC4ANwAyACwAIAAwAC4ANwA2ACwAIAAwAC4AOAAsACAAMAAuADcAOAAsACAAMAAuADcANAAsACAAMAAuADYAOQAsACAAMAAuADcAMwAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AcwBcACIALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzACAAKABhACkAXAAiACwAIAAwAC4AMQA1ACwAIAAwAC4AMQA4ACwAIAAwAC4ANQAwACwAIAAwAC4AMgA0ACwAIAAwAC4AMQA3ACwAIAAwAC4AMQAzACwAIAAwAC4AMQA3ACwAIAAwAC4AMQA4ACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQA7ACAARgByAGEAYwBHAEEAUwBNAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZAApAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAEQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAMAAuADAANwAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABQAGEAZABkAG8AYwBrAFwAIgAsACAAMAAsACAAMAAuADIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAMAAuADMALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMQA3ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIAAnAEEAbgBuAHUAYQBsACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABpAG0AZQAgAHMAcABlAG4AdAAgAHAAZQByACAAYQByAGUAYQAnACAAcgBvAHcAIABhAHMAIAB0AGgAaQBzACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAaQBzACAAaQBuACAAdABoAGUAIAB0AGEAYgBsAGUAIAB0AGkAdABsAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHIAZQBhAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAFMAaABlAGQAXAAiACwAIABcACIARgBlAGUAZABwAGEAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAxADoAIABHAHIAYQB6AGUAZAAgAE8AbgBsAHkAXAAiACwAIAAwAC4AOAA5ACwAIAAwAC4AMQAxACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMgA6ACAATwBuACAAZgBlAGUAZABwAGEAZAAgAGYAbwByACAAPAAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAPAAzACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADcAOQAsACAAMAAuADEAMQAsACAAMAAuADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADMAOgAgAFAAYQBzAHQAdQByAGUALQBnAHIAYQB6AGUAZAAgADMALQA5ACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADUAMwA0ACwAIAAwAC4AMQAxACwAIAAwAC4AMwA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAA0ADoAIABaAGUAcgBvACAAZwByAGEAegBpAG4AZwBcACIALAAgADAALAAgADAALgAxADEALAAgADAALgA4ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgADwAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXABuAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBQAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcAG4ARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABNAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADcANQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AFwAbgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AZQB0ACAAZQBuAGUAcgBnAHkAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAgAC8AIABrAGcAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMwAuADAANQA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXABuAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBFAEMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcARABNAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQA4AC4ANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AFwAbgBFAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAdQBzAGUAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAA4ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBfAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAxADEAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAXwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHoAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4ARgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBDAF8AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQALgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAFwAbgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADIAIABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAzACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARABhAGkAcgB5ACAAQwBhAHQAdABsAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAzAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAxADIANAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAMQAyADQAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANAAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAMQAyADQAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGQAYQB5AHMAKQBcAG4ATgBfAGoAMwA1ACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADMANQAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABkAGEAeQBzACkAXABuAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoAMQAyADQALAAgAE0AXwBqADEAMgA0ACwAIABEAF8AagAxADIANAAsACAATgBfAGoAMwA1ACwAIABNAF8AagAzADUALAAgAEQAXwBqADMANQAsACAARABQAFcAXwBqADMANQAsACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUALABcAG4AIAAgACAAIAAoACgATgBfAGoAMQAyADQAIAAqACAATQBfAGoAMQAyADQAIAAqACAARABfAGoAMQAyADQAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAF8AagAzADUAIAAqACAARABfAGoAMwA1ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAIAAqACAARABQAFcAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAFAAVwBfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADEAMgA0AFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMQAyADQAXAAiACwAIABcACIAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMQAyADQAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADMANQBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMwA1AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagAzADUAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAFAAVwBfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBEAFAAVwAnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25829,9 +25829,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25848,9 +25848,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>